--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1379,6 +1379,27 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1789423736725</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>(Shop)No.3 LBO Y-X0911 -T1 Drain Line 신설 작업</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(Shop)No.3 LBO Y-X0911 -T1 Drain Line 신설 작업</t>
+          <t>(SHOP)No.3 LBO Y-X0911 -T1 Drain Line 신설 작업</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(제작)C8601 안전바</t>
+          <t>(SHOP)C8601 안전바</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,6 +1400,27 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1789540286529</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7B/L DMDS DRUM(3개)운반 작업_지게차</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,6 +1421,27 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1789609247309</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7B/L DMDS DRUM(3개)운반 작업_지게차</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1402,11 +1402,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1789540286529</v>
+        <v>1789609247309</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1416,27 +1416,6 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
-        <is>
-          <t>긴급</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>1789609247309</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>7B/L DMDS DRUM(3개)운반 작업_지게차</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
         <is>
           <t>긴급</t>
         </is>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,6 +1421,27 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1789617998186</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Y-X9111-P03A 배관 Steam Tracing 철거 작업</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1442,27 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1791240682434</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UC공정 고압 Pump Panel 차양막 철거 작업</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1463,6 +1463,27 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1791240985311</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>(제작)No.1 LBO Y-X0355 M/U용 BFW Line Pinhole수리 작업</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1484,6 +1484,27 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1791241000230</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>(제작)No.3 LBO Y-X0911 -T1 BTM Drain Line 신설 작업</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1505,6 +1505,27 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1791241084155</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Y-X9111-D03 개방청소 작업</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -1507,7 +1507,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1791241084155</v>
+        <v>1791241097122</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,6 +1526,27 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1791241107717</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>W26AZ5985</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>W26AZ5985</t>
+          <t>Y-X9111-P03A 전,후단 배관 재질 변경 교체 작업(기존 배관 철거)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,27 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1791241162773</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DS-C3501B 1st 2nd 3rd N2 Blind Open 작업</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,6 +1568,27 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1791241176595</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DS-F3305 C,E Bank F/O By-Pass Sol’ Valve 수리 작업</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,27 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1791241186784</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DS-C3501B 1st, 2nd, 3rd  Suction Strainer 청소 작업</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,6 +1610,27 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1791241200305</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>No.1 LBO 풍향계 수리 작업</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,6 +1631,27 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1791241272862</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>No.3LBO Filetr 접근 금지용 차단봉 설치 작업</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,6 +1652,27 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1791444891258</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>No.1 LBO Steam Leak 수리 작업 (Tracing)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1673,6 +1673,27 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1792396369724</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DS-E3310B HOT BOLTING 작업</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,6 +1694,27 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1792396384914</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DS-E3310B HOT BOLTING 작업</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/memo_db.xlsx
+++ b/memo_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1715,6 +1715,27 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1792562245333</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VD-F1102A Filter 청소 작업</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
